--- a/evaluation/accuracy_metric_based/OLS_Regression_Feature_Analysis_hit@5.xlsx
+++ b/evaluation/accuracy_metric_based/OLS_Regression_Feature_Analysis_hit@5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,370 +453,408 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gini Item</t>
+          <t>const</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.546763049236594</v>
+        <v>41699304620.0976</v>
       </c>
       <c r="C2" t="n">
-        <v>6.231606615108269e-06</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
+        <v>0.80416878209806</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KS Statistic of sensitive attribute</t>
+          <t>Dataset_ml1m</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4408078835009135</v>
+        <v>27507447966.72452</v>
       </c>
       <c r="C3" t="n">
-        <v>8.596591100967817e-36</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
+        <v>0.8041687820976956</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Overestimation Unfairness of sensitive attribute</t>
+          <t>Dataset_BX</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2914264858811659</v>
+        <v>27507447966.61755</v>
       </c>
       <c r="C4" t="n">
-        <v>7.035677742418623e-07</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
+        <v>0.8041687820984377</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Rating per Item</t>
+          <t>Model Name_FOCF</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2488210810923321</v>
+        <v>18221771153.32562</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01022124005887518</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
+        <v>0.8041687820964875</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Difference between Sensitive Attribute Percentage</t>
+          <t>Model Name_PFCN_MLP</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1894205001752478</v>
+        <v>18221771153.15858</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1363847630317341</v>
+        <v>0.8041687820982473</v>
       </c>
       <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Generalized Cross Entropy</t>
+          <t>Model Name_NFCF</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.18157125575435</v>
+        <v>18221771153.04324</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03577412901078502</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
+        <v>0.8041687820994616</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mean Rating</t>
+          <t>Differential Fairness of sensitive attribute</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1717554008553814</v>
+        <v>0.2712765201384789</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5741822160042895</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
+        <v>5.261269853731772e-14</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Number of Users</t>
+          <t>Gini Item</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1254435953304924</v>
+        <v>0.2359360654501033</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2020361500002282</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>0.0001676018324917555</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Differential Fairness of sensitive attribute</t>
+          <t>Rating per Item</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1031476130634542</v>
+        <v>0.1648450119694923</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5374017735753032</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+        <v>0.001356877968573941</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rating per User</t>
+          <t>KS Statistic of sensitive attribute</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03531811483490772</v>
+        <v>0.150180630675426</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5861867290397487</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
+        <v>2.407028775202049e-09</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Skewness of Popularity Bias</t>
+          <t>Number of Users</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.001567850702766681</v>
+        <v>0.05282992919754335</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9763349807189233</v>
+        <v>0.2929811891537768</v>
       </c>
       <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Number of Ratings</t>
+          <t>Generalized Cross Entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.007753106883455846</v>
+        <v>0.0472986977370351</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9587263351808206</v>
+        <v>0.1978775221567238</v>
       </c>
       <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Skewness of Long Tail Items</t>
+          <t>Overestimation Unfairness of sensitive attribute</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.0163400758992207</v>
+        <v>0.04497739691499196</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7551993971738867</v>
+        <v>0.2553913015311434</v>
       </c>
       <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Value Unfairness of sensitive attribute</t>
+          <t>Skewness of Popularity Bias</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.02409081571493368</v>
+        <v>0.03162248074623818</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7021988523963768</v>
+        <v>0.274097834775876</v>
       </c>
       <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dataset_BX</t>
+          <t>Mean Rating</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.02785104716500537</v>
+        <v>0.02875434477238261</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8496168886576503</v>
+        <v>0.8603899851831217</v>
       </c>
       <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Standart Deviation of Rating</t>
+          <t>Skewness of Long Tail Items</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.03090422576441999</v>
+        <v>0.00606643925008632</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8450471146786742</v>
+        <v>0.8296775003742043</v>
       </c>
       <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Gini User</t>
+          <t>Rating per User</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.03491013427603572</v>
+        <v>0.005336387379640893</v>
       </c>
       <c r="C18" t="n">
-        <v>0.666280543894218</v>
+        <v>0.8663810368339108</v>
       </c>
       <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Number of Items</t>
+          <t>Number of Ratings</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.1074262433468615</v>
+        <v>-0.01467150863390797</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3545744152046785</v>
+        <v>0.8483598331143329</v>
       </c>
       <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Shape</t>
+          <t>Number of Items</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1298326254792147</v>
+        <v>-0.01991315284898296</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1654394095833721</v>
+        <v>0.6702311735250499</v>
       </c>
       <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sensitive Feature_Gender</t>
+          <t>Standart Deviation of Rating</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.154465595636575</v>
+        <v>-0.02295081127665986</v>
       </c>
       <c r="C21" t="n">
-        <v>0.01215001933907013</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
+        <v>0.7866222621882895</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sensitive Feature_Age</t>
+          <t>Shape</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1660084610183506</v>
+        <v>-0.03829371447221433</v>
       </c>
       <c r="C22" t="n">
-        <v>0.01569417639228231</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
+        <v>0.4139714240199367</v>
+      </c>
+      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Density</t>
+          <t>Difference between Sensitive Attribute Percentage</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.1920396721360664</v>
+        <v>-0.06598469430278966</v>
       </c>
       <c r="C23" t="n">
-        <v>0.08580550293924216</v>
+        <v>0.3268437027493291</v>
       </c>
       <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dataset_ml1m</t>
+          <t>Gini User</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.2926230094899172</v>
+        <v>-0.09557520556642594</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1310462989883689</v>
-      </c>
-      <c r="D24" t="inlineStr"/>
+        <v>0.0249688886881168</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>const</t>
+          <t>Value Unfairness of sensitive attribute</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.3204740566549251</v>
+        <v>-0.1202566784425576</v>
       </c>
       <c r="C25" t="n">
-        <v>0.01182352510263609</v>
+        <v>0.0002595508447702987</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>*</t>
-        </is>
-      </c>
+          <t>***</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Density</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>-0.1808324811066227</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.002544954583323742</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Sensitive Feature_Age</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-87428523739.9176</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8041687820981194</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sensitive Feature_Gender</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>-87428523739.94202</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8041687820980659</v>
+      </c>
+      <c r="D28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
